--- a/hourly datasets/cap_gen_year18final.xlsx
+++ b/hourly datasets/cap_gen_year18final.xlsx
@@ -485,7 +485,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>0.1003266167401247</v>
+        <v>0.09722469506970693</v>
       </c>
     </row>
     <row r="3">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1205989937732461</v>
+        <v>0.1167241401340968</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
@@ -503,7 +503,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>0.2209256105133708</v>
+        <v>0.2139488352038038</v>
       </c>
     </row>
     <row r="4">
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0922334969654254</v>
+        <v>0.0871465743487711</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
@@ -521,7 +521,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>0.1925601137055501</v>
+        <v>0.184371269418478</v>
       </c>
     </row>
     <row r="5">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.05455858099938535</v>
+        <v>0.04704694072316027</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
@@ -539,7 +539,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>0.15488519773951</v>
+        <v>0.1442716357928672</v>
       </c>
     </row>
     <row r="6">
@@ -549,25 +549,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03399105017831703</v>
+        <v>0.02454219472489527</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002063161373095052</v>
+        <v>0.00129955744446644</v>
       </c>
       <c r="D6" t="n">
-        <v>5.108590596214622</v>
+        <v>4.498206812948045</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01793130077484841</v>
+        <v>0.01563271173779913</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02994497435746121</v>
+        <v>0.02199306611143747</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0380371259991736</v>
+        <v>0.02709132333835292</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1343176669184417</v>
+        <v>0.1217668897946022</v>
       </c>
     </row>
     <row r="7">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02098329472509189</v>
+        <v>0.01039851805848148</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
@@ -585,7 +585,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>0.1213099114652166</v>
+        <v>0.1076232131281884</v>
       </c>
     </row>
     <row r="8">
@@ -595,25 +595,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01766329170384317</v>
+        <v>0.007049723999319156</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001525793020750666</v>
+        <v>0.0008770591117357203</v>
       </c>
       <c r="D8" t="n">
-        <v>2.288135697225182</v>
+        <v>1.340971977588277</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002831795691038407</v>
+        <v>0.0004099029207113442</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01467106096328796</v>
+        <v>0.005329285706147346</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02065552244439854</v>
+        <v>0.008770162292490899</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1179899084439679</v>
+        <v>0.1042744190690261</v>
       </c>
     </row>
     <row r="9">
@@ -623,25 +623,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01370593639939178</v>
+        <v>0.00228202414813422</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001325405845022589</v>
+        <v>0.0006062304569284877</v>
       </c>
       <c r="D9" t="n">
-        <v>1.845308043302414</v>
+        <v>0.8414303095977618</v>
       </c>
       <c r="E9" t="n">
-        <v>0.004891630035760213</v>
+        <v>0.0002013097598203872</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0111056660067547</v>
+        <v>0.001092540678776066</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01630620679202887</v>
+        <v>0.003471507617492299</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1140325531395165</v>
+        <v>0.09950671921784116</v>
       </c>
     </row>
     <row r="10">
@@ -651,25 +651,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.01456505654627893</v>
+        <v>0.002978547705221489</v>
       </c>
       <c r="C10" t="n">
-        <v>0.001243506905066848</v>
+        <v>0.0005944475848975192</v>
       </c>
       <c r="D10" t="n">
-        <v>1.927075274408629</v>
+        <v>0.9131399692592982</v>
       </c>
       <c r="E10" t="n">
-        <v>0.001565032143305553</v>
+        <v>0.0002369875564983031</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01212681971998573</v>
+        <v>0.001812743174649154</v>
       </c>
       <c r="G10" t="n">
-        <v>0.01700329337257235</v>
+        <v>0.004144352235793939</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1148916732864036</v>
+        <v>0.1002032427749284</v>
       </c>
     </row>
     <row r="11">
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02944881224271728</v>
+        <v>0.02899014710368282</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
@@ -687,7 +687,7 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>0.129775428982842</v>
+        <v>0.1262148421733897</v>
       </c>
     </row>
     <row r="12">
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.05493462039451719</v>
+        <v>0.0529379858805234</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
@@ -705,7 +705,7 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>0.1552612371346419</v>
+        <v>0.1501626809502303</v>
       </c>
     </row>
     <row r="13">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.07136870849472941</v>
+        <v>0.06912928560149105</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
@@ -723,7 +723,7 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>0.1716953252348541</v>
+        <v>0.166353980671198</v>
       </c>
     </row>
     <row r="14">
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.08071366564040153</v>
+        <v>0.07824521106970876</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
@@ -741,7 +741,7 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>0.1810402823805262</v>
+        <v>0.1754699061394157</v>
       </c>
     </row>
     <row r="15">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.08688589785266318</v>
+        <v>0.08479971537069807</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
@@ -759,7 +759,7 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>0.1872125145927879</v>
+        <v>0.182024410440405</v>
       </c>
     </row>
     <row r="16">
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.09136261360814441</v>
+        <v>0.08908023591557311</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
@@ -777,7 +777,7 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>0.1916892303482691</v>
+        <v>0.1863049309852801</v>
       </c>
     </row>
     <row r="17">
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.09470325513716944</v>
+        <v>0.09230493782501978</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
@@ -795,7 +795,7 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>0.1950298718772941</v>
+        <v>0.1895296328947267</v>
       </c>
     </row>
     <row r="18">
@@ -805,22 +805,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.1003266167401247</v>
+        <v>-0.09722469506970693</v>
       </c>
       <c r="C18" t="n">
-        <v>0.008832477172191365</v>
+        <v>0.008409259772674881</v>
       </c>
       <c r="D18" t="n">
-        <v>-17.67940362634218</v>
+        <v>-17.65603677286866</v>
       </c>
       <c r="E18" t="n">
-        <v>0.02639662674569922</v>
+        <v>0.02620686010310385</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1176697865311915</v>
+        <v>-0.1137333486968525</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.08298344694905865</v>
+        <v>-0.08071604144256156</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.09734546563161187</v>
+        <v>0.09460801470659216</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
@@ -841,7 +841,7 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>0.1976720823717366</v>
+        <v>0.1918327097762991</v>
       </c>
     </row>
     <row r="20">
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.09783008745779838</v>
+        <v>0.09533428464933529</v>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
@@ -859,7 +859,7 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>0.1981567041979231</v>
+        <v>0.1925589797190422</v>
       </c>
     </row>
     <row r="21">
@@ -869,25 +869,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.1038767265330956</v>
+        <v>0.1013617839163738</v>
       </c>
       <c r="C21" t="n">
-        <v>0.00672076562751971</v>
+        <v>0.006406046496880733</v>
       </c>
       <c r="D21" t="n">
-        <v>307728840990.1163</v>
+        <v>303538551204.9787</v>
       </c>
       <c r="E21" t="n">
-        <v>0.03162607564290397</v>
+        <v>0.03254354934914507</v>
       </c>
       <c r="F21" t="n">
-        <v>0.09067776039653325</v>
+        <v>0.08878011427273352</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1170756926696575</v>
+        <v>0.1139434535600137</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2042033432732203</v>
+        <v>0.1985864789860807</v>
       </c>
     </row>
     <row r="22">
@@ -897,25 +897,25 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.1090740696573277</v>
+        <v>0.1056018200464093</v>
       </c>
       <c r="C22" t="n">
-        <v>0.006553932167117952</v>
+        <v>0.006348060092790516</v>
       </c>
       <c r="D22" t="n">
-        <v>391349497938.6056</v>
+        <v>386688194095.6295</v>
       </c>
       <c r="E22" t="n">
-        <v>0.03407191299841043</v>
+        <v>0.03443440292403278</v>
       </c>
       <c r="F22" t="n">
-        <v>0.09619808977674633</v>
+        <v>0.09312956329553491</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1219500495379095</v>
+        <v>0.118074076797284</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2094006863974524</v>
+        <v>0.2028265151161163</v>
       </c>
     </row>
     <row r="23">
@@ -925,7 +925,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.1124025969882497</v>
+        <v>0.1091579251636534</v>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
@@ -933,7 +933,7 @@
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>0.2127292137283744</v>
+        <v>0.2063826202333603</v>
       </c>
     </row>
     <row r="24">
@@ -943,25 +943,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.1144932298472833</v>
+        <v>0.1118824584073603</v>
       </c>
       <c r="C24" t="n">
-        <v>0.00675977884241839</v>
+        <v>0.006409813306489555</v>
       </c>
       <c r="D24" t="n">
-        <v>513288001324.6094</v>
+        <v>507545030758.347</v>
       </c>
       <c r="E24" t="n">
-        <v>0.03725583779306802</v>
+        <v>0.03686068746401567</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1012186060912258</v>
+        <v>0.09929374296023223</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1277678536033409</v>
+        <v>0.1244711738544884</v>
       </c>
       <c r="H24" t="n">
-        <v>0.214819846587408</v>
+        <v>0.2091071534770673</v>
       </c>
     </row>
     <row r="25">
@@ -971,25 +971,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1162575148829573</v>
+        <v>0.1143719126155704</v>
       </c>
       <c r="C25" t="n">
-        <v>0.006596353122314789</v>
+        <v>0.006377538339582502</v>
       </c>
       <c r="D25" t="n">
-        <v>390053106657.634</v>
+        <v>385803775580.9987</v>
       </c>
       <c r="E25" t="n">
-        <v>0.03780639053908534</v>
+        <v>0.03993630778628472</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1033050339947416</v>
+        <v>0.1018482894317137</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1292099957711725</v>
+        <v>0.1268955357994268</v>
       </c>
       <c r="H25" t="n">
-        <v>0.216584131623082</v>
+        <v>0.2115966076852774</v>
       </c>
     </row>
     <row r="26">
@@ -999,15 +999,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.1219701721120768</v>
-      </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
+        <v>0.1191300638104152</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.00645347923935998</v>
+      </c>
+      <c r="D26" t="n">
+        <v>29.22075332213035</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.03517329711761505</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.1064569488526228</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.1318031787682075</v>
+      </c>
       <c r="H26" t="n">
-        <v>0.2222967888522016</v>
+        <v>0.2163547588801221</v>
       </c>
     </row>
     <row r="27">
@@ -1017,25 +1027,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.123586615344692</v>
+        <v>0.1215534101473791</v>
       </c>
       <c r="C27" t="n">
-        <v>0.006945215237562263</v>
+        <v>0.006647010617579855</v>
       </c>
       <c r="D27" t="n">
-        <v>493671805455.4334</v>
+        <v>489408581040.4033</v>
       </c>
       <c r="E27" t="n">
-        <v>0.04689485811807125</v>
+        <v>0.04614153518039658</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1099444188436101</v>
+        <v>0.1084956100646745</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1372288118457747</v>
+        <v>0.134611210230084</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2239132320848167</v>
+        <v>0.218778105217086</v>
       </c>
     </row>
     <row r="28">
@@ -1045,25 +1055,25 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.1296757909902669</v>
+        <v>0.1266201198949974</v>
       </c>
       <c r="C28" t="n">
-        <v>0.007319432262642567</v>
+        <v>0.007082936442796564</v>
       </c>
       <c r="D28" t="n">
-        <v>27.59098710759789</v>
+        <v>27.44547413485671</v>
       </c>
       <c r="E28" t="n">
-        <v>0.07420003887153313</v>
+        <v>0.07204617305198914</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1153069884658215</v>
+        <v>0.112714695193138</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1440445935147124</v>
+        <v>0.1405255445968566</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2300024077303915</v>
+        <v>0.2238448149647043</v>
       </c>
     </row>
     <row r="29">
@@ -1073,25 +1083,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.0155674419619808</v>
+        <v>0.005137530727604524</v>
       </c>
       <c r="C29" t="n">
-        <v>0.001829527819614971</v>
+        <v>0.0004901598918710756</v>
       </c>
       <c r="D29" t="n">
-        <v>2.379153924950491</v>
+        <v>1.547718928136511</v>
       </c>
       <c r="E29" t="n">
-        <v>0.03488855226974073</v>
+        <v>0.03470654957203678</v>
       </c>
       <c r="F29" t="n">
-        <v>0.01196016692585762</v>
+        <v>0.004176346518054911</v>
       </c>
       <c r="G29" t="n">
-        <v>0.01917471699810374</v>
+        <v>0.006098714937154153</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1158940587021055</v>
+        <v>0.1023622257973115</v>
       </c>
     </row>
   </sheetData>

--- a/hourly datasets/cap_gen_year18final.xlsx
+++ b/hourly datasets/cap_gen_year18final.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,6 +466,11 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>first_seen_iter</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>coef_pos</t>
         </is>
       </c>
@@ -477,7 +482,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>0.2245269717902801</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
@@ -485,7 +490,10 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>0.09722469506970693</v>
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.09387367713920358</v>
       </c>
     </row>
     <row r="3">
@@ -495,7 +503,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1167241401340968</v>
+        <v>0.3828067755153524</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
@@ -503,7 +511,10 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>0.2139488352038038</v>
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.2521534808642759</v>
       </c>
     </row>
     <row r="4">
@@ -513,7 +524,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0871465743487711</v>
+        <v>0.4384412293573837</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
@@ -521,7 +532,10 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>0.184371269418478</v>
+        <v>16</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.3077879347063073</v>
       </c>
     </row>
     <row r="5">
@@ -531,7 +545,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.04704694072316027</v>
+        <v>0.4041750078179385</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
@@ -539,7 +553,10 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>0.1442716357928672</v>
+        <v>47</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.273521713166862</v>
       </c>
     </row>
     <row r="6">
@@ -549,25 +566,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02454219472489527</v>
+        <v>0.3783730286822662</v>
       </c>
       <c r="C6" t="n">
-        <v>0.00129955744446644</v>
+        <v>0.004608508475548069</v>
       </c>
       <c r="D6" t="n">
-        <v>4.498206812948045</v>
+        <v>7.020418356363916</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01563271173779913</v>
+        <v>0.159998995286481</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02199306611143747</v>
+        <v>0.03014629992140593</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02709132333835292</v>
+        <v>0.04822358981061486</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1217668897946022</v>
+        <v>47</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.2477197340311897</v>
       </c>
     </row>
     <row r="7">
@@ -577,7 +597,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01039851805848148</v>
+        <v>0.3614945420993934</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
@@ -585,7 +605,10 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>0.1076232131281884</v>
+        <v>47</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.2308412474483169</v>
       </c>
     </row>
     <row r="8">
@@ -595,25 +618,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.007049723999319156</v>
+        <v>0.3204693311086299</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0008770591117357203</v>
+        <v>0.005314647246453518</v>
       </c>
       <c r="D8" t="n">
-        <v>1.340971977588277</v>
+        <v>-6.80938569565772</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0004099029207113442</v>
+        <v>0.0004350927884245076</v>
       </c>
       <c r="F8" t="n">
-        <v>0.005329285706147346</v>
+        <v>-0.04012258105877015</v>
       </c>
       <c r="G8" t="n">
-        <v>0.008770162292490899</v>
+        <v>-0.01927608716597206</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1042744190690261</v>
+        <v>47</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.1898160364575534</v>
       </c>
     </row>
     <row r="9">
@@ -623,25 +649,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.00228202414813422</v>
+        <v>0.3135519275432526</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0006062304569284877</v>
+        <v>0.005573887756125962</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8414303095977618</v>
+        <v>-7.238680570798281</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0002013097598203872</v>
+        <v>0.0002123051413826675</v>
       </c>
       <c r="F9" t="n">
-        <v>0.001092540678776066</v>
+        <v>-0.05274594638738133</v>
       </c>
       <c r="G9" t="n">
-        <v>0.003471507617492299</v>
+        <v>-0.03088188317239614</v>
       </c>
       <c r="H9" t="n">
-        <v>0.09950671921784116</v>
+        <v>47</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.1828986328921761</v>
       </c>
     </row>
     <row r="10">
@@ -651,25 +680,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.002978547705221489</v>
+        <v>0.3154798571434367</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0005944475848975192</v>
+        <v>0.005429365071526313</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9131399692592982</v>
+        <v>-7.000741270592478</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0002369875564983031</v>
+        <v>0.0002492382139577463</v>
       </c>
       <c r="F10" t="n">
-        <v>0.001812743174649154</v>
+        <v>-0.04920641674247618</v>
       </c>
       <c r="G10" t="n">
-        <v>0.004144352235793939</v>
+        <v>-0.02791043140930262</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1002032427749284</v>
+        <v>47</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.1848265624923602</v>
       </c>
     </row>
     <row r="11">
@@ -679,7 +711,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02899014710368282</v>
+        <v>0.2716268925208621</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
@@ -687,7 +719,10 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>0.1262148421733897</v>
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.1409735978697857</v>
       </c>
     </row>
     <row r="12">
@@ -697,7 +732,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.0529379858805234</v>
+        <v>0.2998874164047751</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
@@ -705,7 +740,10 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>0.1501626809502303</v>
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.1692341217536986</v>
       </c>
     </row>
     <row r="13">
@@ -715,7 +753,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.06912928560149105</v>
+        <v>0.3191181284388743</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
@@ -723,7 +761,10 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>0.166353980671198</v>
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.1884648337877979</v>
       </c>
     </row>
     <row r="14">
@@ -733,7 +774,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.07824521106970876</v>
+        <v>0.3284892515744379</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
@@ -741,7 +782,10 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>0.1754699061394157</v>
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.1978359569233614</v>
       </c>
     </row>
     <row r="15">
@@ -751,7 +795,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.08479971537069807</v>
+        <v>0.337005338878739</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
@@ -759,7 +803,10 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>0.182024410440405</v>
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.2063520442276625</v>
       </c>
     </row>
     <row r="16">
@@ -769,7 +816,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.08908023591557311</v>
+        <v>0.3423281873621768</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
@@ -777,7 +824,10 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>0.1863049309852801</v>
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.2116748927111003</v>
       </c>
     </row>
     <row r="17">
@@ -787,7 +837,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.09230493782501978</v>
+        <v>0.3462701030263776</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
@@ -795,7 +845,10 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>0.1895296328947267</v>
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.2156168083753011</v>
       </c>
     </row>
     <row r="18">
@@ -805,24 +858,27 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.09722469506970693</v>
+        <v>0.1306532946510765</v>
       </c>
       <c r="C18" t="n">
-        <v>0.008409259772674881</v>
+        <v>0.008415976433835164</v>
       </c>
       <c r="D18" t="n">
-        <v>-17.65603677286866</v>
+        <v>-17.67013903866169</v>
       </c>
       <c r="E18" t="n">
-        <v>0.02620686010310385</v>
+        <v>0.02622779209999131</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1137333486968525</v>
+        <v>-0.1138241900296775</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.08071604144256156</v>
+        <v>-0.08078051112422495</v>
       </c>
       <c r="H18" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -833,7 +889,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.09460801470659216</v>
+        <v>0.3477910972403849</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
@@ -841,7 +897,10 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>0.1918327097762991</v>
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.2171378025893085</v>
       </c>
     </row>
     <row r="20">
@@ -851,7 +910,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.09533428464933529</v>
+        <v>0.3497267379995148</v>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
@@ -859,7 +918,10 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>0.1925589797190422</v>
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.2190734433484383</v>
       </c>
     </row>
     <row r="21">
@@ -869,25 +931,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.1013617839163738</v>
+        <v>0.3558405136063065</v>
       </c>
       <c r="C21" t="n">
-        <v>0.006406046496880733</v>
+        <v>0.006402572719615945</v>
       </c>
       <c r="D21" t="n">
-        <v>303538551204.9787</v>
+        <v>303508061373.3088</v>
       </c>
       <c r="E21" t="n">
-        <v>0.03254354934914507</v>
+        <v>0.03253499750179622</v>
       </c>
       <c r="F21" t="n">
-        <v>0.08878011427273352</v>
+        <v>0.08871761891258338</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1139434535600137</v>
+        <v>0.1138673229642185</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1985864789860807</v>
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.2251872189552301</v>
       </c>
     </row>
     <row r="22">
@@ -897,25 +962,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.1056018200464093</v>
+        <v>0.3605561042588827</v>
       </c>
       <c r="C22" t="n">
-        <v>0.006348060092790516</v>
+        <v>0.006344396580936454</v>
       </c>
       <c r="D22" t="n">
-        <v>386688194095.6295</v>
+        <v>386644194552.2482</v>
       </c>
       <c r="E22" t="n">
-        <v>0.03443440292403278</v>
+        <v>0.03442313558825781</v>
       </c>
       <c r="F22" t="n">
-        <v>0.09312956329553491</v>
+        <v>0.09306082151644604</v>
       </c>
       <c r="G22" t="n">
-        <v>0.118074076797284</v>
+        <v>0.1179909525121177</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2028265151161163</v>
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.2299028096078063</v>
       </c>
     </row>
     <row r="23">
@@ -925,7 +993,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.1091579251636534</v>
+        <v>0.366494272504916</v>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
@@ -933,7 +1001,10 @@
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>0.2063826202333603</v>
+        <v>1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.2358409778538395</v>
       </c>
     </row>
     <row r="24">
@@ -943,25 +1014,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.1118824584073603</v>
+        <v>0.3705595033552231</v>
       </c>
       <c r="C24" t="n">
-        <v>0.006409813306489555</v>
+        <v>0.006401022682102487</v>
       </c>
       <c r="D24" t="n">
-        <v>507545030758.347</v>
+        <v>507468704966.098</v>
       </c>
       <c r="E24" t="n">
-        <v>0.03686068746401567</v>
+        <v>0.03681807967696227</v>
       </c>
       <c r="F24" t="n">
-        <v>0.09929374296023223</v>
+        <v>0.09915194066466047</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1244711738544884</v>
+        <v>0.1242948512566761</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2091071534770673</v>
+        <v>1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.2399062087041467</v>
       </c>
     </row>
     <row r="25">
@@ -971,25 +1045,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1143719126155704</v>
+        <v>0.3756690625359697</v>
       </c>
       <c r="C25" t="n">
-        <v>0.006377538339582502</v>
+        <v>0.006359652092383957</v>
       </c>
       <c r="D25" t="n">
-        <v>385803775580.9987</v>
+        <v>385736495051.6444</v>
       </c>
       <c r="E25" t="n">
-        <v>0.03993630778628472</v>
+        <v>0.03986376968920082</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1018482894317137</v>
+        <v>0.1016028019121907</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1268955357994268</v>
+        <v>0.1265797950693363</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2115966076852774</v>
+        <v>1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.2450157678848932</v>
       </c>
     </row>
     <row r="26">
@@ -999,25 +1076,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.1191300638104152</v>
+        <v>0.3804272767783108</v>
       </c>
       <c r="C26" t="n">
-        <v>0.00645347923935998</v>
+        <v>0.006431785661208992</v>
       </c>
       <c r="D26" t="n">
-        <v>29.22075332213035</v>
+        <v>29.16605759867794</v>
       </c>
       <c r="E26" t="n">
-        <v>0.03517329711761505</v>
+        <v>0.03507575141497425</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1064569488526228</v>
+        <v>0.1061383114954591</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1318031787682075</v>
+        <v>0.1313993396965572</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2163547588801221</v>
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.2497739821272344</v>
       </c>
     </row>
     <row r="27">
@@ -1027,25 +1107,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1215534101473791</v>
+        <v>0.3844750707539301</v>
       </c>
       <c r="C27" t="n">
-        <v>0.006647010617579855</v>
+        <v>0.006611266884637074</v>
       </c>
       <c r="D27" t="n">
-        <v>489408581040.4033</v>
+        <v>489303102547.3177</v>
       </c>
       <c r="E27" t="n">
-        <v>0.04614153518039658</v>
+        <v>0.04586687827575667</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1084956100646745</v>
+        <v>0.108012072955991</v>
       </c>
       <c r="G27" t="n">
-        <v>0.134611210230084</v>
+        <v>0.1339872886642812</v>
       </c>
       <c r="H27" t="n">
-        <v>0.218778105217086</v>
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.2538217761028536</v>
       </c>
     </row>
     <row r="28">
@@ -1055,25 +1138,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.1266201198949974</v>
+        <v>0.3944861727214528</v>
       </c>
       <c r="C28" t="n">
-        <v>0.007082936442796564</v>
+        <v>0.007088593740274836</v>
       </c>
       <c r="D28" t="n">
-        <v>27.44547413485671</v>
+        <v>27.46739544007624</v>
       </c>
       <c r="E28" t="n">
-        <v>0.07204617305198914</v>
+        <v>0.07210371791864409</v>
       </c>
       <c r="F28" t="n">
-        <v>0.112714695193138</v>
+        <v>0.1128047229049536</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1405255445968566</v>
+        <v>0.1406377854471735</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2238448149647043</v>
+        <v>2</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.2638328780703764</v>
       </c>
     </row>
     <row r="29">
@@ -1083,25 +1169,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.005137530727604524</v>
+        <v>0.360290048526527</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0004901598918710756</v>
+        <v>0.003856855462052193</v>
       </c>
       <c r="D29" t="n">
-        <v>1.547718928136511</v>
+        <v>1.927481045249206</v>
       </c>
       <c r="E29" t="n">
-        <v>0.03470654957203678</v>
+        <v>0.8004120760354835</v>
       </c>
       <c r="F29" t="n">
-        <v>0.004176346518054911</v>
+        <v>-0.001074513047647795</v>
       </c>
       <c r="G29" t="n">
-        <v>0.006098714937154153</v>
+        <v>0.01405329048899553</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1023622257973115</v>
+        <v>47</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.2296367538754505</v>
       </c>
     </row>
   </sheetData>
